--- a/etf_holdings/2026-10-08_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-08_00403A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:30</t>
+          <t>2026-10-08 23:52:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0%2585</t>
+          <t>-1.35%2550</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2585</v>
+        <v>2550</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13.75%7,700,000</t>
+          <t>13.68%7,700,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.75%</t>
+          <t>13.68%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:30</t>
+          <t>2026-10-08 23:52:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.38%1305</t>
+          <t>-2.68%1270</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1305</v>
+        <v>1270</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.03%7,800,000</t>
+          <t>6.90%7,800,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.03%</t>
+          <t>6.90%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:30</t>
+          <t>2026-10-08 23:52:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.73%4835</t>
+          <t>-3%4690</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4835</v>
+        <v>4690</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.51%1,950,000</t>
+          <t>6.37%1,950,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.51%</t>
+          <t>6.37%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:30</t>
+          <t>2026-10-08 23:52:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.75%5950</t>
+          <t>+0.84%6000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5950</v>
+        <v>6000</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.75%1,400,000</t>
+          <t>5.85%1,400,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.75%</t>
+          <t>5.85%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:30</t>
+          <t>2026-10-08 23:52:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-3.88%6805</t>
+          <t>+5.29%7165</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.88%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6805</v>
+        <v>7165</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.24%1,115,000</t>
+          <t>5.57%1,115,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.24%</t>
+          <t>5.57%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:30</t>
+          <t>2026-10-08 23:52:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-3.8%3545</t>
+          <t>-2.96%3440</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-2.96%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3545</v>
+        <v>3440</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.14%2,100,000</t>
+          <t>5.03%2,100,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.14%</t>
+          <t>5.03%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:30</t>
+          <t>2026-10-08 23:52:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-2.93%1990</t>
+          <t>-1.26%1965</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1990</v>
+        <v>1965</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.99%2,900,000</t>
+          <t>3.97%2,900,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>3.97%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:30</t>
+          <t>2026-10-08 23:52:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+3.52%647</t>
+          <t>-1.85%635</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+3.52%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.93%8,800,000</t>
+          <t>3.89%8,800,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>3.89%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:30</t>
+          <t>2026-10-08 23:52:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+1.01%8460</t>
+          <t>-1.18%8360</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>8460</v>
+        <v>8360</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.74%640,000</t>
+          <t>3.73%640,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>3.73%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:30</t>
+          <t>2026-10-08 23:52:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.47%5530</t>
+          <t>+0.81%5575</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5530</v>
+        <v>5575</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.55%930,000</t>
+          <t>3.61%930,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.61%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:30</t>
+          <t>2026-10-08 23:52:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+2.8%1100</t>
+          <t>-2.27%1075</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>-2.27%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1100</v>
+        <v>1075</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.38%4,450,000</t>
+          <t>3.33%4,450,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:30</t>
+          <t>2026-10-08 23:52:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1.66%1480</t>
+          <t>-0.34%1475</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-1.66%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.08%3,010,000</t>
+          <t>3.09%3,010,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:30</t>
+          <t>2026-10-08 23:52:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.18%2240</t>
+          <t>0%2240</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.63%1,697,956</t>
+          <t>2.65%1,697,956</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.65%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:30</t>
+          <t>2026-10-08 23:52:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+7.17%314</t>
+          <t>+1.16%1740</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+7.17%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>314</v>
+        <v>1740</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.49%11,500,000</t>
+          <t>2.55%2,100,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.55%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>11500000</v>
+        <v>2100000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:30</t>
+          <t>2026-10-08 23:52:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.99%1720</t>
+          <t>-1.27%310</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1720</v>
+        <v>310</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.38%2,000,000</t>
+          <t>2.48%11,500,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.48%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>2000000</v>
+        <v>11500000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:31</t>
+          <t>2026-10-08 23:52:58</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-0.43%2315</t>
+          <t>+1.94%2360</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2315</v>
+        <v>2360</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.33%1,460,000</t>
+          <t>2.40%1,460,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:31</t>
+          <t>2026-10-08 23:52:58</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.71%2015</t>
+          <t>+2.73%2070</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.71%</t>
+          <t>+2.73%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2015</v>
+        <v>2070</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.23%1,600,000</t>
+          <t>2.31%1,600,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.31%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:31</t>
+          <t>2026-10-08 23:52:58</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+2.81%1645</t>
+          <t>+3.95%1710</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+2.81%</t>
+          <t>+3.95%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1645</v>
+        <v>1710</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.05%1,800,000</t>
+          <t>2.14%1,800,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:31</t>
+          <t>2026-10-08 23:52:58</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.68%148.5</t>
+          <t>-0.67%147.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>148.5</v>
+        <v>147.5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.05%20,000,000</t>
+          <t>2.06%20,000,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:31</t>
+          <t>2026-10-08 23:52:58</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+0.83%1215</t>
+          <t>-1.49%17485</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1215</v>
+        <v>17485</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.34%1,600,000</t>
+          <t>1.43%117,500</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1600000</v>
+        <v>117500</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:31</t>
+          <t>2026-10-08 23:52:58</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-6.51%17750</t>
+          <t>+3.5%532</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-6.51%</t>
+          <t>+3.5%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>17750</v>
+        <v>532</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.17%95,500</t>
+          <t>1.04%2,800,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>95500</v>
+        <v>2800000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:31</t>
+          <t>2026-10-08 23:52:58</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-2.1%514</t>
+          <t>-2.7%6660</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>514</v>
+        <v>6660</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.99%2,800,000</t>
+          <t>0.93%200,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>2800000</v>
+        <v>200000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:31</t>
+          <t>2026-10-08 23:52:58</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.15%6845</t>
+          <t>+1.67%304.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+1.67%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6845</v>
+        <v>304.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.95%200,000</t>
+          <t>0.85%4,000,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>200000</v>
+        <v>4000000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:31</t>
+          <t>2026-10-08 23:52:58</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+0.5%299.5</t>
+          <t>-7%1130</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>299.5</v>
+        <v>1130</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.83%4,000,000</t>
+          <t>0.63%800,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>4000000</v>
+        <v>800000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:31</t>
+          <t>2026-10-08 23:52:58</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-10%11790</t>
+          <t>-3.46%2370</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>11790</v>
+        <v>2370</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.61%75,000</t>
+          <t>0.58%350,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>75000</v>
+        <v>350000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:31</t>
+          <t>2026-10-08 23:52:58</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+1.66%2455</t>
+          <t>-1.19%249</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+1.66%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2455</v>
+        <v>249</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.59%350,000</t>
+          <t>0.56%3,200,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>350000</v>
+        <v>3200000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:31</t>
+          <t>2026-10-08 23:52:58</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.56%252</t>
+          <t>-9.97%10615</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>-9.97%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>252</v>
+        <v>10615</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.56%3,200,000</t>
+          <t>0.55%75,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>3200000</v>
+        <v>75000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:31</t>
+          <t>2026-10-08 23:52:58</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+0.75%535</t>
+          <t>-2.43%522</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+0.75%</t>
+          <t>-2.43%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:31</t>
+          <t>2026-10-08 23:52:58</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.39%389.5</t>
+          <t>-0.39%388</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.39%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>389.5</v>
+        <v>388</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:31</t>
+          <t>2026-10-08 23:52:58</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+10%1815</t>
+          <t>-1.65%1785</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1815</v>
+        <v>1785</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:32</t>
+          <t>2026-10-08 23:52:59</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-2.49%743</t>
+          <t>+3.21%1285</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>+3.21%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>743</v>
+        <v>1285</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.41%800,000</t>
+          <t>0.43%480,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>800000</v>
+        <v>480000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:32</t>
+          <t>2026-10-08 23:52:59</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2882國泰金</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.89%113</t>
+          <t>-0.94%736</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>113</v>
+        <v>736</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.31%4,000,000</t>
+          <t>0.41%800,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>4000000</v>
+        <v>800000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:32</t>
+          <t>2026-10-08 23:52:59</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>2882國泰金</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.19%1245</t>
+          <t>-2.65%110</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1245</v>
+        <v>110</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.28%320,000</t>
+          <t>0.31%4,000,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>320000</v>
+        <v>4000000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:32</t>
+          <t>2026-10-08 23:52:59</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.42%178.5</t>
+          <t>-3.36%172.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.42%</t>
+          <t>-3.36%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>178.5</v>
+        <v>172.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:32</t>
+          <t>2026-10-08 23:52:59</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.97%1020</t>
+          <t>-0.98%1010</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:32</t>
+          <t>2026-10-08 23:52:59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.41%559</t>
+          <t>-0.18%558</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.41%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:32</t>
+          <t>2026-10-08 23:52:59</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.59%257.5</t>
+          <t>-0.39%256.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>257.5</v>
+        <v>256.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:32</t>
+          <t>2026-10-08 23:52:59</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.33%300</t>
+          <t>-0.83%297.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>300</v>
+        <v>297.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:32</t>
+          <t>2026-10-08 23:52:59</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.93%75.6</t>
+          <t>-1.59%74.4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>-1.59%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>75.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:32</t>
+          <t>2026-10-08 23:52:59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+1.63%250</t>
+          <t>+2.4%256</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+1.63%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:32</t>
+          <t>2026-10-08 23:52:59</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.36%549</t>
+          <t>-2.55%535</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>-2.55%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:32</t>
+          <t>2026-10-08 23:52:59</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,21 +3005,21 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2337旺宏</t>
+          <t>8299群聯</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.26%118</t>
+          <t>0%2060</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.26%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>118</v>
+        <v>2060</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:32</t>
+          <t>2026-10-08 23:52:59</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,21 +3066,21 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>6196帆宣</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.44%2060</t>
+          <t>+0.6%674</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2060</v>
+        <v>674</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:32</t>
+          <t>2026-10-08 23:52:59</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,21 +3127,21 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.06%670</t>
+          <t>+0.16%308</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.06%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>670</v>
+        <v>308</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:32</t>
+          <t>2026-10-08 23:52:59</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,21 +3188,21 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>2049上銀</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.97%307.5</t>
+          <t>-2.92%332.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>307.5</v>
+        <v>332.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:34</t>
+          <t>2026-10-08 23:53:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,21 +3249,21 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2049上銀</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+0.88%342.5</t>
+          <t>-2.92%2330</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>342.5</v>
+        <v>2330</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:34</t>
+          <t>2026-10-08 23:53:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,21 +3310,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>2404漢唐</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+2.13%2400</t>
+          <t>-1.88%1305</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+2.13%</t>
+          <t>-1.88%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2400</v>
+        <v>1305</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:34</t>
+          <t>2026-10-08 23:53:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,21 +3371,21 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2404漢唐</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-0.37%1330</t>
+          <t>+0.68%5925</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>+0.68%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1330</v>
+        <v>5925</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:34</t>
+          <t>2026-10-08 23:53:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,21 +3432,21 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.34%5885</t>
+          <t>-1.39%177</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>5885</v>
+        <v>177</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-08 00:27:34</t>
+          <t>2026-10-08 23:53:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,21 +3493,21 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+1.13%179.5</t>
+          <t>+1.64%744</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>179.5</v>
+        <v>744</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3528,67 +3528,6 @@
         </is>
       </c>
       <c r="M51" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-10-08 00:27:34</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>3711日月光投控</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>-1.61%732</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-1.61%</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>732</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>0%1,000</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>
